--- a/data/Контрольная работа № 1 (Биоинженеры) (Ответы).xlsx
+++ b/data/Контрольная работа № 1 (Биоинженеры) (Ответы).xlsx
@@ -1,52 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Ответы на форму (1)" sheetId="1" r:id="rId5"/>
+    <sheet name="Ответы на форму (1)" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="217">
-  <si>
-    <t>Отметка времени</t>
-  </si>
-  <si>
-    <t>Адрес электронной почты</t>
-  </si>
-  <si>
-    <t>Баллы</t>
-  </si>
-  <si>
-    <t>Найдите себя в списке</t>
-  </si>
-  <si>
-    <t>Что является основным предметом изучения в области аутэкологии?</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="258">
+  <si>
+    <t xml:space="preserve">Отметка времени</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Адрес электронной почты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баллы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Найдите себя в списке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Что является основным предметом изучения в области аутэкологии?</t>
   </si>
   <si>
     <t xml:space="preserve">Какие из следующих утверждений верны для модели логистического роста популяции (модели Ферхюльста)? </t>
   </si>
   <si>
-    <t>Найдите случаи, где говорится об абиотических факторах биогенного происхождения</t>
-  </si>
-  <si>
-    <t>Какие показатели мы будем измерять, если поставим цель описать  ресурсы, с которыми взаимодействуют цветковые растения</t>
-  </si>
-  <si>
-    <t>Найдите утверждения, которые соотносятся с понятием «экотип»</t>
-  </si>
-  <si>
-    <t>Найдите показатели, которые мы будем измерять, если решим изучить витальные факторы, воздействующие на насекомое-вредителя, поражающего сельскохозяйственные культуры</t>
-  </si>
-  <si>
-    <t>В каких случаях может наблюдаться такая связь между значениями экологического фактора и уровнем благосостояния организма, если мы изучаем насекомое, питающееся культурными растениями.</t>
-  </si>
-  <si>
-    <t>1. Если известно, что у некоторого вида оптимальный диапазон по отношению к фактору F1 составляет 10-20, по отношению к фактору F2: 0 - 250, по отношению к фактору F3: 10-20, по отношению к фактору F4: 10-120, по отношению к F5: 3-4. 
+    <t xml:space="preserve">Найдите случаи, где говорится об абиотических факторах биогенного происхождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Какие показатели мы будем измерять, если поставим цель описать  ресурсы, с которыми взаимодействуют цветковые растения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Найдите утверждения, которые соотносятся с понятием «экотип»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Найдите показатели, которые мы будем измерять, если решим изучить витальные факторы, воздействующие на насекомое-вредителя, поражающего сельскохозяйственные культуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В каких случаях может наблюдаться такая связь между значениями экологического фактора и уровнем благосостояния организма, если мы изучаем насекомое, питающееся культурными растениями.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Если известно, что у некоторого вида оптимальный диапазон по отношению к фактору F1 составляет 10-20, по отношению к фактору F2: 0 - 250, по отношению к фактору F3: 10-20, по отношению к фактору F4: 10-120, по отношению к F5: 3-4. 
 Укажите факторы, которые можно назвать лимитирующими с точки зрения закона Либиха, в местообитании, где значения данных факторов варьируют в следующих пределах: 
 F1: 15-18
 F2: 31-33
@@ -55,47 +64,46 @@
 F5: 0-0.1</t>
   </si>
   <si>
-    <t>Укажите, какие причины могут лежать в основе убывания уровня благосостояния организмов в диапазонах пессимума по отношению к температуре.</t>
-  </si>
-  <si>
-    <t>Какие виды могут существовать в средах с экстремально высокими значениями солености  (более 80 промилле)?</t>
-  </si>
-  <si>
-    <t>Пусковым механизмом реактивации (переход от диапаузы к активности) растений в основном является:</t>
+    <t xml:space="preserve">Укажите, какие причины могут лежать в основе убывания уровня благосостояния организмов в диапазонах пессимума по отношению к температуре.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Какие виды могут существовать в средах с экстремально высокими значениями солености  (более 80 промилле)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пусковым механизмом реактивации (переход от диапаузы к активности) растений в основном является:</t>
   </si>
   <si>
     <t xml:space="preserve">При оценке численности популяции рыб в озере отловили 150 особей, пометили их и снова выпустили в водоем. При повторном вылове, с использованием той же методики, выловили 350 рыб из которых 2 было помеченных. Какова приблизительная численность популяции в этом водоеме? </t>
   </si>
   <si>
-    <t>Какой из популяционных показателей может быть близок к нулю в случае полузависимых популяций</t>
+    <t xml:space="preserve">Какой из популяционных показателей может быть близок к нулю в случае полузависимых популяций</t>
   </si>
   <si>
     <t xml:space="preserve">Какие из популяционных группировок могут быть образованы только особями не способными к размножению </t>
   </si>
   <si>
+    <t xml:space="preserve">Найдите тип популяционной группировки, о которой говорится в следующем фрагменте
+Работая с муфлонами, обитающими в горах, мы заметили, что местообитания, пригодные для их существования, разделены обширными участками, не подходящими для этого вида. В каждой из отдельных группировок мы обнаруживали самцов, самок и детенышей разного возраста. Не вызывает сомнения, что отдельные особи могут покидать свои локальные группы и перемещаться в другие группы, преодолевая участки с неблагоприятными условиями. </t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Найдите тип популяционной группировки, о которой говорится в следующем фрагменте
- </t>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Найдите тип популяционной группировки, о которой говорится в следующем фрагменте</t>
     </r>
     <r>
       <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Работая с муфлонами, обитающими в горах, мы заметили, что местообитания, пригодные для их существования, разделены обширными участками, не подходящими для этого вида. В каждой из отдельных группировок мы обнаруживали самцов, самок и детенышей разного возраста. Не вызывает сомнения, что отдельные особи могут покидать свои локальные группы и перемещаться в другие группы, преодолевая участки с неблагоприятными условиями. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Найдите тип популяционной группировки, о которой говорится в следующем фрагменте</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
+        <family val="0"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 Входе хирургической операции была извлечена финна Echinococcus granulosus объемом около 500 мл. Внутри этого образования находились многочисленные вторичные финны, появившиеся в результате почкования первичной финны.  </t>
@@ -103,776 +111,1207 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. Выберите предложения, которые могут быть отнесены к бактерии </t>
     </r>
     <r>
       <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
+        <family val="0"/>
+        <charset val="134"/>
       </rPr>
-      <t>Wolbachia pipientis</t>
+      <t xml:space="preserve">Wolbachia pipientis</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="0"/>
+        <charset val="134"/>
       </rPr>
-      <t>.</t>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
-    <t>Если мы имеем дело с организмом, для которого характерна кривая выживания третьего типа, то какие из приведенных ниже предложений могут быть отнесены к такому организму?</t>
+    <t xml:space="preserve">Если мы имеем дело с организмом, для которого характерна кривая выживания третьего типа, то какие из приведенных ниже предложений могут быть отнесены к такому организму?</t>
   </si>
   <si>
     <t xml:space="preserve">Если для популяции некоторого организма удалось измерить мальтузианский параметр и он составляет r = 0.000231. Найдите утверждения, который можно сделать на основании этой информации. </t>
   </si>
   <si>
-    <t>Представьте, что на некий остров попало 100 особей вида-вселенца, ранее не обитавшего на этой территории. Если известно, что в среднем за минимально возможный промежуток времени (один год) на одну особь в популяции приходится 0.1 потомка, но за тот же промежуток времени удельная смертность составляет 0.01, то сколько особей будет представлено в популяции через 10 лет если учесть, что емкость среды составляет 200000 особей данного вида. Ответ округлите до целых.</t>
-  </si>
-  <si>
-    <t>Какие изменения в популяции могут быть предсказаны, исходя из модели Ферхюльста?</t>
-  </si>
-  <si>
-    <t>Если мы имеем дело со стенотермным организмом (стенобионт в отношении температуры), то какие суждения мы можем сделать относительно этого организма.</t>
-  </si>
-  <si>
-    <t>Если мы сталкиваемся в одном местообитании с двумя криптическими видами (виды, чьи генофонды изолированы, но морфологические отличия между видами незначительны), то с какими экологическими группировками мы можем их перепутать?</t>
+    <t xml:space="preserve">Представьте, что на некий остров попало 100 особей вида-вселенца, ранее не обитавшего на этой территории. Если известно, что в среднем за минимально возможный промежуток времени (один год) на одну особь в популяции приходится 0.1 потомка, но за тот же промежуток времени удельная смертность составляет 0.01, то сколько особей будет представлено в популяции через 10 лет если учесть, что емкость среды составляет 200000 особей данного вида. Ответ округлите до целых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Какие изменения в популяции могут быть предсказаны, исходя из модели Ферхюльста?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если мы имеем дело со стенотермным организмом (стенобионт в отношении температуры), то какие суждения мы можем сделать относительно этого организма.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если мы сталкиваемся в одном местообитании с двумя криптическими видами (виды, чьи генофонды изолированы, но морфологические отличия между видами незначительны), то с какими экологическими группировками мы можем их перепутать?</t>
   </si>
   <si>
     <t xml:space="preserve">Какие из следующих утверждений точно описывают характеристику, именуемую «ёмкостью среды» (K)? </t>
   </si>
   <si>
-    <t>Какие из следующих утверждений точно описывают мальтузианский параметр (r)?</t>
-  </si>
-  <si>
-    <t>1507vlad2007@gmail.com</t>
-  </si>
-  <si>
-    <t>st143210</t>
-  </si>
-  <si>
-    <t>Взаимосвязь организма (вида) с окружающей его абиотической средой.</t>
-  </si>
-  <si>
-    <t>Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., При некотором сочетании параметров модель демонстрирует хаотичное поведение., Это модель динамического процесса первого порядка, Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
-  </si>
-  <si>
-    <t>Площадь субстрата в отношении эпифитного лишайника, Температура в отношении аскариды, Кислород в атмосфере в отношении ели, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Неорганический азот в почве относительно пшеницы</t>
-  </si>
-  <si>
-    <t>Площадь доступного пространства, Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве</t>
-  </si>
-  <si>
-    <t>Группа особей какого-либо вида, обладающих наследуемыми признаками, появившимися в результате действия естественного отбора при разных параметрах среды, Группа особей одного вида, обладающих генетически закреплёнными особенностями, выработавшимися в результате продолжительного воздействия сходных режимов экологических факторов.</t>
-  </si>
-  <si>
-    <t>Обилие паразитоидов, Обилие кормовых растений, Обилие спор бактерий, Температура воздуха, Концентрацию инсектицидов, Уровень освещенности, Концентрацию феромонов</t>
-  </si>
-  <si>
-    <t>Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси ординат отложены значения плодовитости насекомого., Если по оси ординат отложена скорость роста насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
-  </si>
-  <si>
-    <t>F3, F5</t>
-  </si>
-  <si>
-    <t>Испарение воды из тканей, Работа защитных механизмов организма, Денатурация белков, Замерзание воды в клетках, Снижение активности ферментов</t>
-  </si>
-  <si>
-    <t>Осморегуляторы, Виды морского происхождения, Осмоконформеры, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
-  </si>
-  <si>
-    <t>изменение длины светового дня, повышение температуры</t>
-  </si>
-  <si>
-    <t>E (эмиграция)</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция, Микрогемипопуляция</t>
-  </si>
-  <si>
-    <t>Метапопуляция</t>
-  </si>
-  <si>
-    <t>Микропопуляция</t>
-  </si>
-  <si>
-    <t>Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия поселяется в яйцах некоторых насекомых., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>Очень высокая детская смертность., Забота о потомстве выражена слабо., Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Как правило, мелкие организмы., В популяциях должны преобладать молодые особи.</t>
-  </si>
-  <si>
-    <t>Численность популяции демонстрирует экспоненциальный рост., Численность популяции растет или не изменяется, В среднем, рождаемость преобладает над смертностью</t>
-  </si>
-  <si>
-    <t>На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности.</t>
-  </si>
-  <si>
-    <t>Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях.</t>
-  </si>
-  <si>
-    <t>Экотипы, Экологические расы</t>
-  </si>
-  <si>
-    <t>При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
-  </si>
-  <si>
-    <t>Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов.</t>
-  </si>
-  <si>
-    <t>9829910@mail.ru</t>
-  </si>
-  <si>
-    <t>st142998</t>
-  </si>
-  <si>
-    <t>Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Температура в отношении аскариды, Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы</t>
-  </si>
-  <si>
-    <t>Площадь доступного пространства, Концентрация неорганического азота в почве, Концентрация углекислого газа в атмосфере</t>
-  </si>
-  <si>
-    <t>Группа особей одного вида, обладающих генетически закреплёнными особенностями, выработавшимися в результате продолжительного воздействия сходных режимов экологических факторов., Группа особей какого-либо вида, обладающих наследуемыми признаками, появившимися в результате действия естественного отбора при разных параметрах среды</t>
-  </si>
-  <si>
-    <t>Концентрацию инсектицидов, Обилие спор бактерий, Температура воздуха, Уровень освещенности, Обилие паразитоидов, Обилие кормовых растений</t>
-  </si>
-  <si>
-    <t>Если по оси абсцисс отложены значения витального фактора, Если по оси абсцисс отложены значения некоторого первичного периодического фактора., Если по оси абсцисс отложены значения температуры.</t>
-  </si>
-  <si>
-    <t>Снижение активности ферментов, Испарение воды из тканей, Работа защитных механизмов организма, Денатурация белков</t>
-  </si>
-  <si>
-    <t>Осмоконформеры, Осморегуляторы, Виды морского происхождения, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
-  </si>
-  <si>
-    <t>изменение длины светового дня</t>
-  </si>
-  <si>
-    <t>Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца.</t>
-  </si>
-  <si>
-    <t>Очень высокая детская смертность., Как правило, мелкие организмы., В популяциях должны преобладать молодые особи., Высокая плодовитость., Забота о потомстве выражена слабо., Коэффициент смертности максимален для молодых особей.</t>
-  </si>
-  <si>
-    <t>В среднем, рождаемость преобладает над смертностью, Численность популяции растет или не изменяется, Численность популяции демонстрирует экспоненциальный рост.</t>
-  </si>
-  <si>
-    <t>При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности</t>
-  </si>
-  <si>
-    <t>У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Этот организм может обитать только в очень ограниченном наборе местообитаний.</t>
-  </si>
-  <si>
-    <t>Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
-  </si>
-  <si>
-    <t>Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
-  </si>
-  <si>
-    <t>ilukgerasimov@gmail.com</t>
-  </si>
-  <si>
-    <t>st144664</t>
-  </si>
-  <si>
-    <t>Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., Это модель динамического процесса первого порядка, Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
-  </si>
-  <si>
-    <t>Неорганический азот в почве относительно пшеницы, Кислород в атмосфере в отношении ели, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Субстрат в отношении эпилитного лишайника</t>
-  </si>
-  <si>
-    <t>Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Площадь доступного пространства</t>
-  </si>
-  <si>
-    <t>Температура воздуха, Обилие паразитоидов, Обилие кормовых растений, Обилие спор бактерий, Уровень освещенности, Кислород в атмосфере</t>
-  </si>
-  <si>
-    <t>Снижение активности ферментов, Денатурация белков, Замерзание воды в клетках, Испарение воды из тканей</t>
-  </si>
-  <si>
-    <t>Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде, Виды морского происхождения, Осмоконформеры</t>
-  </si>
-  <si>
-    <t>I (иммиграция)</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция, Временная популяция, Периодически возникающая популяция</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция</t>
-  </si>
-  <si>
-    <t>Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>Высокая плодовитость., Коэффициент смертности максимален для молодых особей., В популяциях должны преобладать старые особи., Забота о потомстве выражена слабо.</t>
-  </si>
-  <si>
-    <t>Численность популяции растет или не изменяется, Численность популяции демонстрирует экспоненциальный рост., В среднем, рождаемость преобладает над смертностью</t>
-  </si>
-  <si>
-    <t>На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, В определенный момент произойдет стабилизация численности популяции</t>
-  </si>
-  <si>
-    <t>Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Этот организм менее конкурентоспособен, чем эвритермный вид.</t>
-  </si>
-  <si>
-    <t>При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство.</t>
-  </si>
-  <si>
-    <t>Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K).</t>
-  </si>
-  <si>
-    <t>st142730@student.spbu.ru</t>
-  </si>
-  <si>
-    <t>st142730</t>
-  </si>
-  <si>
-    <t>Неорганический азот в почве относительно пшеницы, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Соленость в отношении улитки-литторины, Температура в отношении аскариды, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели</t>
-  </si>
-  <si>
-    <t>Обилие насекомых фитофагов, питающиеся этими растениями, Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве</t>
-  </si>
-  <si>
-    <t>Группа особей одного вида, обладающих генетически закреплёнными особенностями, выработавшимися в результате продолжительного воздействия сходных режимов экологических факторов.</t>
-  </si>
-  <si>
-    <t>Обилие спор бактерий, Температура воздуха, Концентрацию удобрений, способствующих росту пищевого растения, Уровень освещенности, Обилие паразитоидов, Обилие кормовых растений</t>
-  </si>
-  <si>
-    <t>Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси абсцисс отложены значения витального фактора, Если по оси ординат отложены значения плодовитости насекомого., Если по оси ординат отложена скорость роста насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
-  </si>
-  <si>
-    <t>Работа защитных механизмов организма, Испарение воды из тканей, Замерзание воды в клетках, Денатурация белков, Снижение активности ферментов</t>
-  </si>
-  <si>
-    <t>Виды морского происхождения, Осморегуляторы</t>
-  </si>
-  <si>
-    <t>B (рождаемость)</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция, Гемипопуляция</t>
-  </si>
-  <si>
-    <t>Микрогемипопуляция, Гемипопуляция</t>
-  </si>
-  <si>
-    <t>Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>Коэффициент смертности остается постоянным на всем протяжении жизни., В популяциях должны преобладать молодые особи., Высокая плодовитость., Как правило, мелкие организмы., Забота о потомстве выражена слабо., Очень высокая детская смертность.</t>
-  </si>
-  <si>
-    <t>В среднем, рождаемость преобладает над смертностью, Численность популяции растет или не изменяется</t>
-  </si>
-  <si>
-    <t>При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции, На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности</t>
-  </si>
-  <si>
-    <t>Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
-  </si>
-  <si>
-    <t>Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов.</t>
-  </si>
-  <si>
-    <t>a.e.luneva@gmail.com</t>
-  </si>
-  <si>
-    <t>st143996</t>
-  </si>
-  <si>
-    <t>Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., При некотором сочетании параметров модель демонстрирует хаотичное поведение., Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды</t>
-  </si>
-  <si>
-    <t>Кислород в атмосфере в отношении ели, Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Неорганический азот в почве относительно пшеницы, Площадь субстрата в отношении эпифитного лишайника</t>
-  </si>
-  <si>
-    <t>Обилие кормовых растений, Кислород в атмосфере, Уровень освещенности, Температура воздуха</t>
-  </si>
-  <si>
-    <t>Снижение активности ферментов, Денатурация белков, Работа защитных механизмов организма, Испарение воды из тканей, Замерзание воды в клетках</t>
-  </si>
-  <si>
-    <t>Осморегуляторы, Виды пресноводного происхождения</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция, Гемипопуляция, Микрогемипопуляция</t>
-  </si>
-  <si>
-    <t>Гемипопуляция, Микрогемипопуляция</t>
-  </si>
-  <si>
-    <t>Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Забота о потомстве выражена слабо., Как правило, мелкие организмы., Очень высокая детская смертность.</t>
-  </si>
-  <si>
-    <t>При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции</t>
-  </si>
-  <si>
-    <t>У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., Этот организм может обитать только в очень ограниченном наборе местообитаний.</t>
-  </si>
-  <si>
-    <t>Экологические расы, Экотипы</t>
-  </si>
-  <si>
-    <t>Высокое значение этого параметра характерно для видов-оппортунистов., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K).</t>
-  </si>
-  <si>
-    <t>kk8725493@gmail.com</t>
-  </si>
-  <si>
-    <t>st143705</t>
-  </si>
-  <si>
-    <t>Взаимосвязь организма (вида) с окружающей его абиотической средой., Процессы круговорота веществ и потоки энергии в биосфере.</t>
-  </si>
-  <si>
-    <t>Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Кислород в атмосфере в атмосфере в отношении взрослой блохи</t>
-  </si>
-  <si>
-    <t>Обилие спор бактерий, Обилие кормовых растений, Обилие паразитоидов</t>
-  </si>
-  <si>
-    <t>Если по оси ординат отложены значения плодовитости насекомого., Если по оси ординат отложена скорость роста насекомого., Если по оси абсцисс отложены значения некоторого первичного периодического фактора., Если по оси абсцисс отложены значения температуры.</t>
-  </si>
-  <si>
-    <t>Денатурация белков, Замерзание воды в клетках, Снижение активности ферментов</t>
-  </si>
-  <si>
-    <t>Осмоконформеры, Осморегуляторы, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
-  </si>
-  <si>
-    <t>изменение длины светового дня, повышение влажности, повышение температуры</t>
-  </si>
-  <si>
-    <t>Гемипопуляция</t>
-  </si>
-  <si>
-    <t>Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих.</t>
-  </si>
-  <si>
-    <t>Высокая плодовитость., Забота о потомстве выражена слабо., Очень высокая детская смертность., В популяциях должны преобладать старые особи., Как правило, мелкие организмы., Коэффициент смертности максимален для молодых особей.</t>
-  </si>
-  <si>
-    <t>Численность популяции демонстрирует экспоненциальный рост., В среднем, рождаемость преобладает над смертностью, Численность популяции растет или не изменяется</t>
-  </si>
-  <si>
-    <t>На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции</t>
-  </si>
-  <si>
-    <t>У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма</t>
-  </si>
-  <si>
-    <t>Экологические расы, Жизненные формы</t>
-  </si>
-  <si>
-    <t>При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
-  </si>
-  <si>
-    <t>Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Высокое значение этого параметра характерно для видов-оппортунистов.</t>
-  </si>
-  <si>
-    <t>st143728@student.spbu.ru</t>
-  </si>
-  <si>
-    <t>st143728</t>
-  </si>
-  <si>
-    <t>Кислород в атмосфере в отношении ели, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Площадь субстрата в отношении эпифитного лишайника, Неорганический азот в почве относительно пшеницы</t>
-  </si>
-  <si>
-    <t>Площадь доступного пространства, Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Температура воздуха</t>
-  </si>
-  <si>
-    <t>Обилие кормовых растений, Температура воздуха, Обилие спор бактерий, Обилие паразитоидов, Кислород в атмосфере</t>
-  </si>
-  <si>
-    <t>Испарение воды из тканей, Денатурация белков, Снижение активности ферментов, Замерзание воды в клетках</t>
-  </si>
-  <si>
-    <t>Виды пресноводного происхождения, Осморегуляторы</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция, Гемипопуляция, Звисимая популяция, Микрогемипопуляция</t>
-  </si>
-  <si>
-    <t>Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>В популяциях должны преобладать молодые особи., Коэффициент смертности максимален для молодых особей., Очень высокая детская смертность., Забота о потомстве выражена слабо., Высокая плодовитость., Как правило, мелкие организмы.</t>
-  </si>
-  <si>
-    <t>Численность популяции растет или не изменяется, В среднем, рождаемость преобладает над смертностью, Численность популяции демонстрирует экспоненциальный рост.</t>
-  </si>
-  <si>
-    <t>При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, Численность популяции изменяется не предсказуемо., В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности</t>
-  </si>
-  <si>
-    <t>Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется.</t>
-  </si>
-  <si>
-    <t>Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Высокое значение этого параметра характерно для видов-оппортунистов.</t>
-  </si>
-  <si>
-    <t>st142999@student.spbu.ru</t>
-  </si>
-  <si>
-    <t>st142999</t>
-  </si>
-  <si>
-    <t>Рост популяции является неограниченным и экспоненциальным., При некотором сочетании параметров модель демонстрирует хаотичное поведение.</t>
-  </si>
-  <si>
-    <t>Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Температура в отношении аскариды</t>
-  </si>
-  <si>
-    <t>Концентрация неорганического азота в почве, Концентрация углекислого газа в атмосфере, Площадь доступного пространства</t>
-  </si>
-  <si>
-    <t>Обилие кормовых растений, Концентрацию феромонов, Обилие паразитоидов, Обилие спор бактерий</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>Замерзание воды в клетках, Денатурация белков, Снижение активности ферментов</t>
-  </si>
-  <si>
-    <t>Виды пресноводного происхождения</t>
-  </si>
-  <si>
-    <t>Микрогемипопуляция</t>
-  </si>
-  <si>
-    <t>Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>Как правило, мелкие организмы., Забота о потомстве выражена слабо., Очень высокая детская смертность., Высокая плодовитость., В популяциях должны преобладать молодые особи., Коэффициент смертности максимален для молодых особей.</t>
-  </si>
-  <si>
-    <t>На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции</t>
-  </si>
-  <si>
-    <t>Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Ёмкость среды может изменяться в зависимости от времени года или внешних условий.</t>
-  </si>
-  <si>
-    <t>st144243@student.spbu.ru</t>
-  </si>
-  <si>
-    <t>st144243</t>
-  </si>
-  <si>
-    <t>Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в отношении ели, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в атмосфере в отношении взрослой блохи</t>
-  </si>
-  <si>
-    <t>Кислород в атмосфере, Обилие кормовых растений, Температура воздуха</t>
-  </si>
-  <si>
-    <t>Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси ординат отложены значения плодовитости насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
-  </si>
-  <si>
-    <t>Денатурация белков, Замерзание воды в клетках, Испарение воды из тканей, Снижение активности ферментов, Активация иммунной системы при высокой температуре окружающей среды</t>
-  </si>
-  <si>
-    <t>повышение влажности, повышение температуры, изменение длины светового дня</t>
-  </si>
-  <si>
-    <t>Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих.</t>
-  </si>
-  <si>
-    <t>Коэффициент смертности максимален для старых особей., Высокая плодовитость., Забота о потомстве выражена слабо., В популяциях должны преобладать молодые особи., Очень высокая детская смертность., Как правило, мелкие организмы., В популяциях должны быть представлены только молодые особи.</t>
-  </si>
-  <si>
-    <t>При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, В определенный момент произойдет стабилизация численности популяции</t>
-  </si>
-  <si>
-    <t>Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., Этот организм менее конкурентоспособен, чем эвритермный вид.</t>
-  </si>
-  <si>
-    <t>При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды может изменяться в зависимости от времени года или внешних условий.</t>
-  </si>
-  <si>
-    <t>Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K).</t>
-  </si>
-  <si>
-    <t>st143761@student.spbu.ru</t>
-  </si>
-  <si>
-    <t>st143761</t>
-  </si>
-  <si>
-    <t>Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели, Кислород в атмосфере в атмосфере в отношении взрослой блохи</t>
-  </si>
-  <si>
-    <t>Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси абсцисс отложены значения обилия паразитоидов</t>
-  </si>
-  <si>
-    <t>Снижение активности ферментов, Испарение воды из тканей, Денатурация белков, Замерзание воды в клетках</t>
-  </si>
-  <si>
-    <t>Осмоконформеры, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
-  </si>
-  <si>
-    <t>Псевдопопуляция, Временная популяция</t>
-  </si>
-  <si>
-    <t>Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций млекопитающих., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>В популяциях должны преобладать молодые особи., Забота о потомстве выражена слабо., Как правило, мелкие организмы., Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Очень высокая детская смертность.</t>
-  </si>
-  <si>
-    <t>Численность популяции растет или не изменяется, В среднем, рождаемость преобладает над смертностью</t>
-  </si>
-  <si>
-    <t>Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма</t>
-  </si>
-  <si>
-    <t>Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется.</t>
-  </si>
-  <si>
-    <t>Высокое значение этого параметра характерно для видов-оппортунистов., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
-  </si>
-  <si>
-    <t>st106945@spbu.ru</t>
-  </si>
-  <si>
-    <t>st106945</t>
-  </si>
-  <si>
-    <t>Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., При некотором сочетании параметров модель демонстрирует хаотичное поведение., Это модель динамического процесса первого порядка, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
-  </si>
-  <si>
-    <t>Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Соленость в отношении мирацидия сосальщиков</t>
-  </si>
-  <si>
-    <t>Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Обилие растений эпифитов, Обилие насекомых фитофагов, питающиеся этими растениями</t>
-  </si>
-  <si>
-    <t>Группа особей какого-либо вида, обладающих наследуемыми признаками, появившимися в результате действия естественного отбора при разных параметрах среды, Группы особей какого-либо вида, обладающих признаками, появившимися в результате физиологического ответа на влияния разных параметров среды.</t>
-  </si>
-  <si>
-    <t>Температура воздуха, Обилие паразитоидов, Концентрацию инсектицидов</t>
-  </si>
-  <si>
-    <t>F3, F4, F5</t>
-  </si>
-  <si>
-    <t>Накопление антифризов в клетках при экстремально низких значениях температуры, Снижение активности ферментов, Работа защитных механизмов организма, Испарение воды из тканей</t>
-  </si>
-  <si>
-    <t>Теплокровные организмы, Виды пресноводного происхождения, Осморегуляторы</t>
-  </si>
-  <si>
-    <t>повышение температуры, повышение влажности, изменение длины светового дня</t>
-  </si>
-  <si>
-    <t>Поселения, Независимая популяция, Временная популяция, Периодически возникающая популяция, Микропопуляция, Микрогемипопуляция, Метапопуляция</t>
-  </si>
-  <si>
-    <t>Независимая популяция, Метапопуляция, Поселение</t>
-  </si>
-  <si>
-    <t>Временная популяция, Микропопуляция</t>
-  </si>
-  <si>
-    <t>Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций птиц., Эта бактерия поселяется в яйцах некоторых насекомых.</t>
-  </si>
-  <si>
-    <t>Как правило, мелкие организмы., Очень высокая детская смертность., Коэффициент смертности остается постоянным на всем протяжении жизни., Высокая плодовитость., В популяциях должны преобладать молодые особи., Забота о потомстве выражена слабо.</t>
-  </si>
-  <si>
-    <t>Популяция замкнутая, Для данного вида характерна кривая выживания третьего типа., В популяции смертность стремится к нулю, Численность популяции демонстрирует экспоненциальный рост., Численность популяции растет или не изменяется, В популяции присутствует эмиграция, В среднем, рождаемость преобладает над смертностью, В популяции присутствует иммиграция, Численность популяции падает</t>
-  </si>
-  <si>
-    <t>894, 100, 10000, 631, 246</t>
-  </si>
-  <si>
-    <t>При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., Численность популяции изменяется не предсказуемо., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, Численность популяции изменяется циклически с периодом значительно превышающем продолжительность жизни особей., Популяция демонстрирует неограниченный рост численности.</t>
-  </si>
-  <si>
-    <t>Этот организм может обитать только в очень ограниченном наборе местообитаний., Этот организм менее конкурентоспособен, чем эвритермный вид., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма., Этот организм может жить только при высокой температуре, Этот организм может жить только при низкой температуре, Этот организм может жить только при средних значениях температуры.</t>
-  </si>
-  <si>
-    <t>Гемипопуляции, Микрогемипопоуляции, Экотипы, Жизненные формы, Гильдии, Эврибионты и стенобионты, Экологические расы</t>
-  </si>
-  <si>
-    <t>Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это точка, в которой рождаемость в популяции максимальна, а смертность минимальна., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
-  </si>
-  <si>
-    <t>Высокое значение этого параметра характерно для видов-оппортунистов., Это максимальная удельная скорость роста численности популяции в условиях, когда ресурсы ограничены и действует внутривидовая конкуренция., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
+    <t xml:space="preserve">Какие из следующих утверждений точно описывают мальтузианский параметр (r)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1507vlad2007@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взаимосвязь организма (вида) с окружающей его абиотической средой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., При некотором сочетании параметров модель демонстрирует хаотичное поведение., Это модель динамического процесса первого порядка, Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь субстрата в отношении эпифитного лишайника, Температура в отношении аскариды, Кислород в атмосфере в отношении ели, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Неорганический азот в почве относительно пшеницы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь доступного пространства, Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа особей какого-либо вида, обладающих наследуемыми признаками, появившимися в результате действия естественного отбора при разных параметрах среды, Группа особей одного вида, обладающих генетически закреплёнными особенностями, выработавшимися в результате продолжительного воздействия сходных режимов экологических факторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие паразитоидов, Обилие кормовых растений, Обилие спор бактерий, Температура воздуха, Концентрацию инсектицидов, Уровень освещенности, Концентрацию феромонов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси ординат отложены значения плодовитости насекомого., Если по оси ординат отложена скорость роста насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3, F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Испарение воды из тканей, Работа защитных механизмов организма, Денатурация белков, Замерзание воды в клетках, Снижение активности ферментов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осморегуляторы, Виды морского происхождения, Осмоконформеры, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">изменение длины светового дня, повышение температуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E (эмиграция)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция, Микрогемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Метапопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микропопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия поселяется в яйцах некоторых насекомых., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очень высокая детская смертность., Забота о потомстве выражена слабо., Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Как правило, мелкие организмы., В популяциях должны преобладать молодые особи.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Численность популяции демонстрирует экспоненциальный рост., Численность популяции растет или не изменяется, В среднем, рождаемость преобладает над смертностью</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Экотипы, Экологические расы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9829910@mail.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Температура в отношении аскариды, Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь доступного пространства, Концентрация неорганического азота в почве, Концентрация углекислого газа в атмосфере</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа особей одного вида, обладающих генетически закреплёнными особенностями, выработавшимися в результате продолжительного воздействия сходных режимов экологических факторов., Группа особей какого-либо вида, обладающих наследуемыми признаками, появившимися в результате действия естественного отбора при разных параметрах среды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрацию инсектицидов, Обилие спор бактерий, Температура воздуха, Уровень освещенности, Обилие паразитоидов, Обилие кормовых растений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси абсцисс отложены значения витального фактора, Если по оси абсцисс отложены значения некоторого первичного периодического фактора., Если по оси абсцисс отложены значения температуры.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение активности ферментов, Испарение воды из тканей, Работа защитных механизмов организма, Денатурация белков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осмоконформеры, Осморегуляторы, Виды морского происхождения, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">изменение длины светового дня</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очень высокая детская смертность., Как правило, мелкие организмы., В популяциях должны преобладать молодые особи., Высокая плодовитость., Забота о потомстве выражена слабо., Коэффициент смертности максимален для молодых особей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В среднем, рождаемость преобладает над смертностью, Численность популяции растет или не изменяется, Численность популяции демонстрирует экспоненциальный рост.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Этот организм может обитать только в очень ограниченном наборе местообитаний.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilukgerasimov@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st144664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., Это модель динамического процесса первого порядка, Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неорганический азот в почве относительно пшеницы, Кислород в атмосфере в отношении ели, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Субстрат в отношении эпилитного лишайника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Площадь доступного пространства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Температура воздуха, Обилие паразитоидов, Обилие кормовых растений, Обилие спор бактерий, Уровень освещенности, Кислород в атмосфере</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение активности ферментов, Денатурация белков, Замерзание воды в клетках, Испарение воды из тканей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде, Виды морского происхождения, Осмоконформеры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I (иммиграция)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция, Временная популяция, Периодически возникающая популяция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокая плодовитость., Коэффициент смертности максимален для молодых особей., В популяциях должны преобладать старые особи., Забота о потомстве выражена слабо.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Численность популяции растет или не изменяется, Численность популяции демонстрирует экспоненциальный рост., В среднем, рождаемость преобладает над смертностью</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, В определенный момент произойдет стабилизация численности популяции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Этот организм менее конкурентоспособен, чем эвритермный вид.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142730@student.spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неорганический азот в почве относительно пшеницы, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Соленость в отношении улитки-литторины, Температура в отношении аскариды, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие насекомых фитофагов, питающиеся этими растениями, Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа особей одного вида, обладающих генетически закреплёнными особенностями, выработавшимися в результате продолжительного воздействия сходных режимов экологических факторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие спор бактерий, Температура воздуха, Концентрацию удобрений, способствующих росту пищевого растения, Уровень освещенности, Обилие паразитоидов, Обилие кормовых растений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси абсцисс отложены значения витального фактора, Если по оси ординат отложены значения плодовитости насекомого., Если по оси ординат отложена скорость роста насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Работа защитных механизмов организма, Испарение воды из тканей, Замерзание воды в клетках, Денатурация белков, Снижение активности ферментов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Виды морского происхождения, Осморегуляторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B (рождаемость)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция, Гемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микрогемипопуляция, Гемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент смертности остается постоянным на всем протяжении жизни., В популяциях должны преобладать молодые особи., Высокая плодовитость., Как правило, мелкие организмы., Забота о потомстве выражена слабо., Очень высокая детская смертность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В среднем, рождаемость преобладает над смертностью, Численность популяции растет или не изменяется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции, На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a.e.luneva@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., При некотором сочетании параметров модель демонстрирует хаотичное поведение., Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кислород в атмосфере в отношении ели, Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Неорганический азот в почве относительно пшеницы, Площадь субстрата в отношении эпифитного лишайника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие кормовых растений, Кислород в атмосфере, Уровень освещенности, Температура воздуха</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение активности ферментов, Денатурация белков, Работа защитных механизмов организма, Испарение воды из тканей, Замерзание воды в клетках</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осморегуляторы, Виды пресноводного происхождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция, Гемипопуляция, Микрогемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гемипопуляция, Микрогемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Забота о потомстве выражена слабо., Как правило, мелкие организмы., Очень высокая детская смертность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., Этот организм может обитать только в очень ограниченном наборе местообитаний.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Экологические расы, Экотипы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокое значение этого параметра характерно для видов-оппортунистов., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kk8725493@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взаимосвязь организма (вида) с окружающей его абиотической средой., Процессы круговорота веществ и потоки энергии в биосфере.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Кислород в атмосфере в атмосфере в отношении взрослой блохи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие спор бактерий, Обилие кормовых растений, Обилие паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси ординат отложены значения плодовитости насекомого., Если по оси ординат отложена скорость роста насекомого., Если по оси абсцисс отложены значения некоторого первичного периодического фактора., Если по оси абсцисс отложены значения температуры.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денатурация белков, Замерзание воды в клетках, Снижение активности ферментов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осмоконформеры, Осморегуляторы, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">изменение длины светового дня, повышение влажности, повышение температуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокая плодовитость., Забота о потомстве выражена слабо., Очень высокая детская смертность., В популяциях должны преобладать старые особи., Как правило, мелкие организмы., Коэффициент смертности максимален для молодых особей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Численность популяции демонстрирует экспоненциальный рост., В среднем, рождаемость преобладает над смертностью, Численность популяции растет или не изменяется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Экологические расы, Жизненные формы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Высокое значение этого параметра характерно для видов-оппортунистов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143728@student.spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кислород в атмосфере в отношении ели, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Площадь субстрата в отношении эпифитного лишайника, Неорганический азот в почве относительно пшеницы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь доступного пространства, Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Температура воздуха</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие кормовых растений, Температура воздуха, Обилие спор бактерий, Обилие паразитоидов, Кислород в атмосфере</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Испарение воды из тканей, Денатурация белков, Снижение активности ферментов, Замерзание воды в клетках</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Виды пресноводного происхождения, Осморегуляторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция, Гемипопуляция, Звисимая популяция, Микрогемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В популяциях должны преобладать молодые особи., Коэффициент смертности максимален для молодых особей., Очень высокая детская смертность., Забота о потомстве выражена слабо., Высокая плодовитость., Как правило, мелкие организмы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Численность популяции растет или не изменяется, В среднем, рождаемость преобладает над смертностью, Численность популяции демонстрирует экспоненциальный рост.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, Численность популяции изменяется не предсказуемо., В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Высокое значение этого параметра характерно для видов-оппортунистов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142999@student.spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост популяции является неограниченным и экспоненциальным., При некотором сочетании параметров модель демонстрирует хаотичное поведение.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Температура в отношении аскариды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрация неорганического азота в почве, Концентрация углекислого газа в атмосфере, Площадь доступного пространства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обилие кормовых растений, Концентрацию феромонов, Обилие паразитоидов, Обилие спор бактерий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замерзание воды в клетках, Денатурация белков, Снижение активности ферментов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Виды пресноводного происхождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микрогемипопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Эта бактерия поселяется в яйцах некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Как правило, мелкие организмы., Забота о потомстве выражена слабо., Очень высокая детская смертность., Высокая плодовитость., В популяциях должны преобладать молодые особи., Коэффициент смертности максимален для молодых особей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Ёмкость среды может изменяться в зависимости от времени года или внешних условий.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st144243@student.spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st144243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в отношении ели, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в атмосфере в отношении взрослой блохи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кислород в атмосфере, Обилие кормовых растений, Температура воздуха</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси ординат отложены значения плодовитости насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денатурация белков, Замерзание воды в клетках, Испарение воды из тканей, Снижение активности ферментов, Активация иммунной системы при высокой температуре окружающей среды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">повышение влажности, повышение температуры, изменение длины светового дня</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Эта бактерия поселяется в яйцах некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент смертности максимален для старых особей., Высокая плодовитость., Забота о потомстве выражена слабо., В популяциях должны преобладать молодые особи., Очень высокая детская смертность., Как правило, мелкие организмы., В популяциях должны быть представлены только молодые особи.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, В определенный момент произойдет стабилизация численности популяции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., Этот организм менее конкурентоспособен, чем эвритермный вид.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды может изменяться в зависимости от времени года или внешних условий.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143761@student.spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st143761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели, Кислород в атмосфере в атмосфере в отношении взрослой блохи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси абсцисс отложены значения обилия паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение активности ферментов, Испарение воды из тканей, Денатурация белков, Замерзание воды в клетках</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осмоконформеры, Виды с параметрами внутренней среды, зависящими от концентрации солей в окружающей среде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Псевдопопуляция, Временная популяция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций млекопитающих., Эта бактерия может изменять ход дробления яйца у некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В популяциях должны преобладать молодые особи., Забота о потомстве выражена слабо., Как правило, мелкие организмы., Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Очень высокая детская смертность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Численность популяции растет или не изменяется, В среднем, рождаемость преобладает над смертностью</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот организм может обитать только в очень ограниченном наборе местообитаний., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокое значение этого параметра характерно для видов-оппортунистов., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st106945@spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st106945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., При некотором сочетании параметров модель демонстрирует хаотичное поведение., Это модель динамического процесса первого порядка, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Соленость в отношении мирацидия сосальщиков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Обилие растений эпифитов, Обилие насекомых фитофагов, питающиеся этими растениями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа особей какого-либо вида, обладающих наследуемыми признаками, появившимися в результате действия естественного отбора при разных параметрах среды, Группы особей какого-либо вида, обладающих признаками, появившимися в результате физиологического ответа на влияния разных параметров среды.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Температура воздуха, Обилие паразитоидов, Концентрацию инсектицидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3, F4, F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накопление антифризов в клетках при экстремально низких значениях температуры, Снижение активности ферментов, Работа защитных механизмов организма, Испарение воды из тканей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теплокровные организмы, Виды пресноводного происхождения, Осморегуляторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">повышение температуры, повышение влажности, изменение длины светового дня</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поселения, Независимая популяция, Временная популяция, Периодически возникающая популяция, Микропопуляция, Микрогемипопуляция, Метапопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Независимая популяция, Метапопуляция, Поселение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Временная популяция, Микропопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций птиц., Эта бактерия поселяется в яйцах некоторых насекомых.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Как правило, мелкие организмы., Очень высокая детская смертность., Коэффициент смертности остается постоянным на всем протяжении жизни., Высокая плодовитость., В популяциях должны преобладать молодые особи., Забота о потомстве выражена слабо.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Популяция замкнутая, Для данного вида характерна кривая выживания третьего типа., В популяции смертность стремится к нулю, Численность популяции демонстрирует экспоненциальный рост., Численность популяции растет или не изменяется, В популяции присутствует эмиграция, В среднем, рождаемость преобладает над смертностью, В популяции присутствует иммиграция, Численность популяции падает</t>
+  </si>
+  <si>
+    <t xml:space="preserve">894, 100, 10000, 631, 246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., Численность популяции изменяется не предсказуемо., На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, Численность популяции изменяется циклически с периодом значительно превышающем продолжительность жизни особей., Популяция демонстрирует неограниченный рост численности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот организм может обитать только в очень ограниченном наборе местообитаний., Этот организм менее конкурентоспособен, чем эвритермный вид., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма., Этот организм может жить только при высокой температуре, Этот организм может жить только при низкой температуре, Этот организм может жить только при средних значениях температуры.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гемипопуляции, Микрогемипопоуляции, Экотипы, Жизненные формы, Гильдии, Эврибионты и стенобионты, Экологические расы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это точка, в которой рождаемость в популяции максимальна, а смертность минимальна., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокое значение этого параметра характерно для видов-оппортунистов., Это максимальная удельная скорость роста численности популяции в условиях, когда ресурсы ограничены и действует внутривидовая конкуренция., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142856@student.spbu.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st142856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., Скорость роста популяции равна нулю, когда размер популяции (N) достигает ёмкости среды, Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Соленость в отношении мирацидия сосальщиков, Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрация углекислого газа в атмосфере, Концентрация неорганического азота в почве, Обилие насекомых фитофагов, питающиеся этими растениями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрацию инсектицидов, Обилие паразитоидов, Обилие кормовых растений, Концентрацию удобрений, способствующих росту пищевого растения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если по оси абсцисс отложены значения концентрация инсектицида, Если по оси абсцисс отложены значения витального фактора, Если по оси ординат отложены значения плодовитости насекомого., Если по оси абсцисс отложены значения обилия паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение активности ферментов, Замерзание воды в клетках, Работа защитных механизмов организма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сухопутные виды, Осморегуляторы, Теплокровные организмы, Виды морского происхождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">повышение вариабельности значений экологических факторов, накопление загрязняющих веществ, изменение длины светового дня, повышение влажности, повышение температуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Звисимая популяция, Периодически возникающая популяция, Микропопуляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Временная популяция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Звисимая популяция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент смертности максимален для старых особей., Как правило, мелкие организмы., Высокая плодовитость., Забота о потомстве выражена слабо., В популяциях должны преобладать молодые особи.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот организм менее конкурентоспособен, чем эвритермный вид., Уровень благосостояния у этого организма всегда выше, чем у эвритермного организма, если они обитают при оптимальных условиях., У этого организма величина диапазона толерантности будет меньше, чем у эвритермного организма, Этот организм может обитать только в очень ограниченном наборе местообитаний.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жизненные формы, Гемипопуляции, Экологические расы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ёмкость среды может изменяться в зависимости от времени года или внешних условий., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокое значение этого параметра характерно для видов-оппортунистов., В модели логистического роста популяции этот параметр остаётся постоянным, даже когда размер популяции приближается к ёмкости среды (K)., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">angel.mirnaya@yandex.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st150414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель включает в себя ёмкость среды (K) — максимальный размер популяции, который может поддерживать среда., Это модель динамического процесса первого порядка, Скорость роста популяции максимальна, когда размер популяции (N) значительно превышает ёмкость среды (K)., Динамика роста популяции описывается S-образной (сигмоидной) кривой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Температура в отношении аскариды, Соленость в отношении спороцисты в улитке-литторине, Кислород в атмосфере в атмосфере в отношении взрослой блохи, Кислород в атмосфере в отношении ели, Неорганический азот в почве относительно пшеницы, Площадь субстрата в отношении эпифитного лишайника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрацию инсектицидов, Температура воздуха, Обилие кормовых растений, Обилие спор бактерий, Кислород в атмосфере, Обилие паразитоидов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денатурация белков, Снижение активности ферментов, Замерзание воды в клетках, Испарение воды из тканей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B (рождаемость), D (смертность), E (эмиграция)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эта бактерия поселяется в яйцах некоторых насекомых., Заражение яиц некоторых насекомых вольбахией может приводить к формированию диплоидного яйца после первого митотического деления неоплодотворенного яйца., Эта бактерия может изменять ход дробления яйца у некоторых насекомых., Заражение вольбахией может быть важным фактором, влияющим на половую структуру популяций некоторых членистоногих.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокая плодовитость., Коэффициент смертности максимален для молодых особей., Очень высокая детская смертность., Как правило, мелкие организмы., В популяциях должны преобладать молодые особи., Забота о потомстве выражена слабо.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности., В определенный момент произойдет стабилизация численности популяции, При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., Ёмкость среды может изменяться в зависимости от времени года или внешних условий., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется., Это максимальный размер популяции, который может поддерживаться средой неопределённо долго.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Высокое значение этого параметра характерно для видов-оппортунистов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">polikraspolichka7@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st097958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кислород в атмосфере в атмосфере в отношении взрослой блохи, Неорганический азот в почве относительно пшеницы, Температура в отношении аскариды, Площадь субстрата в отношении эпифитного лишайника, Кислород в атмосфере в отношении ели, Соленость в отношении спороцисты в улитке-литторине</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концентрацию инсектицидов, Температура воздуха, Обилие паразитоидов, Обилие кормовых растений, Обилие спор бактерий, Кислород в атмосфере</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замерзание воды в клетках, Денатурация белков, Снижение активности ферментов, Испарение воды из тканей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E (эмиграция), D (смертность), B (рождаемость)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Как правило, мелкие организмы., Высокая плодовитость., В популяциях должны преобладать молодые особи., Коэффициент смертности максимален для молодых особей., Очень высокая детская смертность., Забота о потомстве выражена слабо.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При определенных значениях мальтузианского параметра могут появляться циклические колебания численности, В определенный момент произойдет стабилизация численности популяции, На ранних этапах возникновения популяции будет наблюдаться практически экспоненциальный рост численности, При определенных значениях мальтузианского параметра должны появляться хаотичные элементы в изменениях численности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это максимальный размер популяции, который может поддерживаться средой неопределённо долго., Ёмкость среды определяется доступностью ресурсов, таких как пища, вода и пространство., При достижении ёмкости среды популяция перестаёт расти, и её численность стабилизируется.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокое значение этого параметра характерно для видов-оппортунистов., Это теоретически возможная максимальная скорость роста популяции на одну особь в идеальных условиях (при неограниченных ресурсах)., Он рассчитывается как разность между удельной рождаемостью и удельной смертностью в отсутствие лимитирующих факторов.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="0&quot; / 25&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="0&quot; / 25&quot;"/>
+    <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+      <family val="0"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="11">
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="18">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="2">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Ответы на форму (1)-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF8F9FA"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF442F65"/>
+      <rgbColor rgb="FF434343"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AC12" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:AC12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="29">
-    <tableColumn name="Отметка времени" id="1"/>
-    <tableColumn name="Адрес электронной почты" id="2"/>
-    <tableColumn name="Баллы" id="3"/>
-    <tableColumn name="Найдите себя в списке" id="4"/>
-    <tableColumn name="Что является основным предметом изучения в области аутэкологии?" id="5"/>
-    <tableColumn name="Какие из следующих утверждений верны для модели логистического роста популяции (модели Ферхюльста)? " id="6"/>
-    <tableColumn name="Найдите случаи, где говорится об абиотических факторах биогенного происхождения" id="7"/>
-    <tableColumn name="Какие показатели мы будем измерять, если поставим цель описать  ресурсы, с которыми взаимодействуют цветковые растения" id="8"/>
-    <tableColumn name="Найдите утверждения, которые соотносятся с понятием «экотип»" id="9"/>
-    <tableColumn name="Найдите показатели, которые мы будем измерять, если решим изучить витальные факторы, воздействующие на насекомое-вредителя, поражающего сельскохозяйственные культуры" id="10"/>
-    <tableColumn name="В каких случаях может наблюдаться такая связь между значениями экологического фактора и уровнем благосостояния организма, если мы изучаем насекомое, питающееся культурными растениями." id="11"/>
-    <tableColumn name="1. Если известно, что у некоторого вида оптимальный диапазон по отношению к фактору F1 составляет 10-20, по отношению к фактору F2: 0 - 250, по отношению к фактору F3: 10-20, по отношению к фактору F4: 10-120, по отношению к F5: 3-4. _x000a_Укажите факторы, которые можно назвать лимитирующими с точки зрения закона Либиха, в местообитании, где значения данных факторов варьируют в следующих пределах: _x000a_F1: 15-18_x000a_F2: 31-33_x000a_F3: 28-50_x000a_F4: 40-100_x000a_F5: 0-0.1" id="12"/>
-    <tableColumn name="Укажите, какие причины могут лежать в основе убывания уровня благосостояния организмов в диапазонах пессимума по отношению к температуре." id="13"/>
-    <tableColumn name="Какие виды могут существовать в средах с экстремально высокими значениями солености  (более 80 промилле)?" id="14"/>
-    <tableColumn name="Пусковым механизмом реактивации (переход от диапаузы к активности) растений в основном является:" id="15"/>
-    <tableColumn name="При оценке численности популяции рыб в озере отловили 150 особей, пометили их и снова выпустили в водоем. При повторном вылове, с использованием той же методики, выловили 350 рыб из которых 2 было помеченных. Какова приблизительная численность популяции в этом водоеме? " id="16"/>
-    <tableColumn name="Какой из популяционных показателей может быть близок к нулю в случае полузависимых популяций" id="17"/>
-    <tableColumn name="Какие из популяционных группировок могут быть образованы только особями не способными к размножению " id="18"/>
-    <tableColumn name="Найдите тип популяционной группировки, о которой говорится в следующем фрагменте_x000a_ _x000a_Работая с муфлонами, обитающими в горах, мы заметили, что местообитания, пригодные для их существования, разделены обширными участками, не подходящими для этого вида. В каждой из отдельных группировок мы обнаруживали самцов, самок и детенышей разного возраста. Не вызывает сомнения, что отдельные особи могут покидать свои локальные группы и перемещаться в другие группы, преодолевая участки с неблагоприятными условиями. " id="19"/>
-    <tableColumn name="Найдите тип популяционной группировки, о которой говорится в следующем фрагменте_x000a__x000a_Входе хирургической операции была извлечена финна Echinococcus granulosus объемом около 500 мл. Внутри этого образования находились многочисленные вторичные финны, появившиеся в результате почкования первичной финны.  " id="20"/>
-    <tableColumn name="1. Выберите предложения, которые могут быть отнесены к бактерии Wolbachia pipientis." id="21"/>
-    <tableColumn name="Если мы имеем дело с организмом, для которого характерна кривая выживания третьего типа, то какие из приведенных ниже предложений могут быть отнесены к такому организму?" id="22"/>
-    <tableColumn name="Если для популяции некоторого организма удалось измерить мальтузианский параметр и он составляет r = 0.000231. Найдите утверждения, который можно сделать на основании этой информации. " id="23"/>
-    <tableColumn name="Представьте, что на некий остров попало 100 особей вида-вселенца, ранее не обитавшего на этой территории. Если известно, что в среднем за минимально возможный промежуток времени (один год) на одну особь в популяции приходится 0.1 потомка, но за тот же промежуток времени удельная смертность составляет 0.01, то сколько особей будет представлено в популяции через 10 лет если учесть, что емкость среды составляет 200000 особей данного вида. Ответ округлите до целых." id="24"/>
-    <tableColumn name="Какие изменения в популяции могут быть предсказаны, исходя из модели Ферхюльста?" id="25"/>
-    <tableColumn name="Если мы имеем дело со стенотермным организмом (стенобионт в отношении температуры), то какие суждения мы можем сделать относительно этого организма." id="26"/>
-    <tableColumn name="Если мы сталкиваемся в одном местообитании с двумя криптическими видами (виды, чьи генофонды изолированы, но морфологические отличия между видами незначительны), то с какими экологическими группировками мы можем их перепутать?" id="27"/>
-    <tableColumn name="Какие из следующих утверждений точно описывают характеристику, именуемую «ёмкостью среды» (K)? " id="28"/>
-    <tableColumn name="Какие из следующих утверждений точно описывают мальтузианский параметр (r)?" id="29"/>
+    <tableColumn id="1" name="Отметка времени"/>
+    <tableColumn id="2" name="Адрес электронной почты"/>
+    <tableColumn id="3" name="Баллы"/>
+    <tableColumn id="4" name="Найдите себя в списке"/>
+    <tableColumn id="5" name="Что является основным предметом изучения в области аутэкологии?"/>
+    <tableColumn id="6" name="Какие из следующих утверждений верны для модели логистического роста популяции (модели Ферхюльста)? "/>
+    <tableColumn id="7" name="Найдите случаи, где говорится об абиотических факторах биогенного происхождения"/>
+    <tableColumn id="8" name="Какие показатели мы будем измерять, если поставим цель описать  ресурсы, с которыми взаимодействуют цветковые растения"/>
+    <tableColumn id="9" name="Найдите утверждения, которые соотносятся с понятием «экотип»"/>
+    <tableColumn id="10" name="Найдите показатели, которые мы будем измерять, если решим изучить витальные факторы, воздействующие на насекомое-вредителя, поражающего сельскохозяйственные культуры"/>
+    <tableColumn id="11" name="В каких случаях может наблюдаться такая связь между значениями экологического фактора и уровнем благосостояния организма, если мы изучаем насекомое, питающееся культурными растениями."/>
+    <tableColumn id="12" name="1. Если известно, что у некоторого вида оптимальный диапазон по отношению к фактору F1 составляет 10-20, по отношению к фактору F2: 0 - 250, по отношению к фактору F3: 10-20, по отношению к фактору F4: 10-120, по отношению к F5: 3-4. &#10;Укажите факторы, которые можно назвать лимитирующими с точки зрения закона Либиха, в местообитании, где значения данных факторов варьируют в следующих пределах: &#10;F1: 15-18&#10;F2: 31-33&#10;F3: 28-50&#10;F4: 40-100&#10;F5: 0-0.1"/>
+    <tableColumn id="13" name="Укажите, какие причины могут лежать в основе убывания уровня благосостояния организмов в диапазонах пессимума по отношению к температуре."/>
+    <tableColumn id="14" name="Какие виды могут существовать в средах с экстремально высокими значениями солености  (более 80 промилле)?"/>
+    <tableColumn id="15" name="Пусковым механизмом реактивации (переход от диапаузы к активности) растений в основном является:"/>
+    <tableColumn id="16" name="При оценке численности популяции рыб в озере отловили 150 особей, пометили их и снова выпустили в водоем. При повторном вылове, с использованием той же методики, выловили 350 рыб из которых 2 было помеченных. Какова приблизительная численность популяции в этом водоеме? "/>
+    <tableColumn id="17" name="Какой из популяционных показателей может быть близок к нулю в случае полузависимых популяций"/>
+    <tableColumn id="18" name="Какие из популяционных группировок могут быть образованы только особями не способными к размножению "/>
+    <tableColumn id="19" name="Найдите тип популяционной группировки, о которой говорится в следующем фрагменте&#10; &#10;Работая с муфлонами, обитающими в горах, мы заметили, что местообитания, пригодные для их существования, разделены обширными участками, не подходящими для этого вида. В каждой из отдельных группировок мы обнаруживали самцов, самок и детенышей разного возраста. Не вызывает сомнения, что отдельные особи могут покидать свои локальные группы и перемещаться в другие группы, преодолевая участки с неблагоприятными условиями. "/>
+    <tableColumn id="20" name="Найдите тип популяционной группировки, о которой говорится в следующем фрагменте&#10;&#10;Входе хирургической операции была извлечена финна Echinococcus granulosus объемом около 500 мл. Внутри этого образования находились многочисленные вторичные финны, появившиеся в результате почкования первичной финны.  "/>
+    <tableColumn id="21" name="1. Выберите предложения, которые могут быть отнесены к бактерии Wolbachia pipientis."/>
+    <tableColumn id="22" name="Если мы имеем дело с организмом, для которого характерна кривая выживания третьего типа, то какие из приведенных ниже предложений могут быть отнесены к такому организму?"/>
+    <tableColumn id="23" name="Если для популяции некоторого организма удалось измерить мальтузианский параметр и он составляет r = 0.000231. Найдите утверждения, который можно сделать на основании этой информации. "/>
+    <tableColumn id="24" name="Представьте, что на некий остров попало 100 особей вида-вселенца, ранее не обитавшего на этой территории. Если известно, что в среднем за минимально возможный промежуток времени (один год) на одну особь в популяции приходится 0.1 потомка, но за тот же промежуток времени удельная смертность составляет 0.01, то сколько особей будет представлено в популяции через 10 лет если учесть, что емкость среды составляет 200000 особей данного вида. Ответ округлите до целых."/>
+    <tableColumn id="25" name="Какие изменения в популяции могут быть предсказаны, исходя из модели Ферхюльста?"/>
+    <tableColumn id="26" name="Если мы имеем дело со стенотермным организмом (стенобионт в отношении температуры), то какие суждения мы можем сделать относительно этого организма."/>
+    <tableColumn id="27" name="Если мы сталкиваемся в одном местообитании с двумя криптическими видами (виды, чьи генофонды изолированы, но морфологические отличия между видами незначительны), то с какими экологическими группировками мы можем их перепутать?"/>
+    <tableColumn id="28" name="Какие из следующих утверждений точно описывают характеристику, именуемую «ёмкостью среды» (K)? "/>
+    <tableColumn id="29" name="Какие из следующих утверждений точно описывают мальтузианский параметр (r)?"/>
   </tableColumns>
-  <tableStyleInfo name="Ответы на форму (1)-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -884,94 +1323,90 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -979,33 +1414,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1018,13 +1444,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1034,15 +1454,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -1050,7 +1468,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -1058,11 +1475,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1071,21 +1488,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AI15"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="25.63"/>
-    <col customWidth="1" min="3" max="3" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="22.88"/>
-    <col customWidth="1" min="5" max="29" width="37.63"/>
-    <col customWidth="1" min="30" max="35" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="5" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="30" style="0" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1174,15 +1593,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2">
-        <v>46077.787572430556</v>
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>46077.7875724306</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4">
-        <v>10.0</v>
+      <c r="C2" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>30</v>
@@ -1220,8 +1639,8 @@
       <c r="O2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="3">
-        <v>24819.0</v>
+      <c r="P2" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>42</v>
@@ -1244,8 +1663,8 @@
       <c r="W2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="3">
-        <v>246.0</v>
+      <c r="X2" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>49</v>
@@ -1263,15 +1682,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="2">
-        <v>46077.80652763889</v>
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>46077.8065276389</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4">
-        <v>11.0</v>
+      <c r="C3" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>55</v>
@@ -1309,8 +1728,8 @@
       <c r="O3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P3" s="3">
-        <v>24819.0</v>
+      <c r="P3" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>42</v>
@@ -1333,8 +1752,8 @@
       <c r="W3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="X3" s="3">
-        <v>246.0</v>
+      <c r="X3" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>67</v>
@@ -1352,15 +1771,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="2">
-        <v>46077.815316099535</v>
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>46077.8153160995</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="4">
-        <v>6.0</v>
+      <c r="C4" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>72</v>
@@ -1398,8 +1817,8 @@
       <c r="O4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="3">
-        <v>498.0</v>
+      <c r="P4" s="3" t="n">
+        <v>498</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>79</v>
@@ -1422,8 +1841,8 @@
       <c r="W4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="X4" s="3">
-        <v>246.0</v>
+      <c r="X4" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>85</v>
@@ -1441,15 +1860,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="2">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
         <v>46077.8202203125</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="4">
-        <v>8.0</v>
+      <c r="C5" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>90</v>
@@ -1487,8 +1906,8 @@
       <c r="O5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="3">
-        <v>24819.0</v>
+      <c r="P5" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>98</v>
@@ -1511,8 +1930,8 @@
       <c r="W5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="X5" s="3">
-        <v>246.0</v>
+      <c r="X5" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>104</v>
@@ -1530,15 +1949,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="2">
-        <v>46077.822751238426</v>
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>46077.8227512384</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="4">
-        <v>11.0</v>
+      <c r="C6" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>108</v>
@@ -1576,8 +1995,8 @@
       <c r="O6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P6" s="3">
-        <v>17550.0</v>
+      <c r="P6" s="3" t="n">
+        <v>17550</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>42</v>
@@ -1600,8 +2019,8 @@
       <c r="W6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="X6" s="3">
-        <v>246.0</v>
+      <c r="X6" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>118</v>
@@ -1619,15 +2038,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="2">
-        <v>46077.82374371528</v>
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>46077.8237437153</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="4">
-        <v>4.0</v>
+      <c r="C7" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>123</v>
@@ -1665,8 +2084,8 @@
       <c r="O7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="P7" s="3">
-        <v>24819.0</v>
+      <c r="P7" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>42</v>
@@ -1689,8 +2108,8 @@
       <c r="W7" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="X7" s="3">
-        <v>246.0</v>
+      <c r="X7" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>135</v>
@@ -1708,15 +2127,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="2">
-        <v>46077.82672006944</v>
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>46077.8267200694</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="4">
-        <v>9.0</v>
+      <c r="C8" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>141</v>
@@ -1754,8 +2173,8 @@
       <c r="O8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P8" s="3">
-        <v>17550.0</v>
+      <c r="P8" s="3" t="n">
+        <v>17550</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>98</v>
@@ -1778,8 +2197,8 @@
       <c r="W8" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="X8" s="3">
-        <v>246.0</v>
+      <c r="X8" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>151</v>
@@ -1797,15 +2216,15 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="2">
-        <v>46077.83304427083</v>
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>46077.8330442708</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="4">
-        <v>13.0</v>
+      <c r="C9" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>155</v>
@@ -1843,8 +2262,8 @@
       <c r="O9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P9" s="3">
-        <v>17550.0</v>
+      <c r="P9" s="3" t="n">
+        <v>17550</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>42</v>
@@ -1867,8 +2286,8 @@
       <c r="W9" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="X9" s="3">
-        <v>246.0</v>
+      <c r="X9" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>166</v>
@@ -1886,15 +2305,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="2">
-        <v>46077.83483283565</v>
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>46077.8348328357</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="4">
-        <v>7.0</v>
+      <c r="C10" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>169</v>
@@ -1932,8 +2351,8 @@
       <c r="O10" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="P10" s="3">
-        <v>24819.0</v>
+      <c r="P10" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>42</v>
@@ -1956,8 +2375,8 @@
       <c r="W10" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="X10" s="3">
-        <v>246.0</v>
+      <c r="X10" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>177</v>
@@ -1975,15 +2394,15 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="2">
-        <v>46077.835548703704</v>
+    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>46077.8355487037</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="4">
-        <v>13.0</v>
+      <c r="C11" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>182</v>
@@ -2021,8 +2440,8 @@
       <c r="O11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="3">
-        <v>24819.0</v>
+      <c r="P11" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>98</v>
@@ -2045,8 +2464,8 @@
       <c r="W11" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="X11" s="3">
-        <v>246.0</v>
+      <c r="X11" s="3" t="n">
+        <v>246</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>166</v>
@@ -2064,15 +2483,15 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="2">
-        <v>46077.85406841435</v>
+    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>46077.8540684144</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="4">
-        <v>1.0</v>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>195</v>
@@ -2110,8 +2529,8 @@
       <c r="O12" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="P12" s="3">
-        <v>24819.0</v>
+      <c r="P12" s="3" t="n">
+        <v>24819</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>98</v>
@@ -2153,10 +2572,301 @@
         <v>216</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>46086.5008101852</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>24819</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="T13" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="X13" s="7" t="n">
+        <v>894</v>
+      </c>
+      <c r="Y13" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA13" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB13" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC13" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="n">
+        <v>46094.0904976852</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="P14" s="12" t="n">
+        <v>24819</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="R14" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="X14" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z14" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC14" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="9"/>
+      <c r="AG14" s="9"/>
+      <c r="AH14" s="9"/>
+      <c r="AI14" s="9"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="n">
+        <v>46094.9831365741</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>24819</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="V15" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="W15" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="X15" s="16" t="n">
+        <v>246</v>
+      </c>
+      <c r="Y15" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z15" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA15" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB15" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="AC15" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="9"/>
+      <c r="AI15" s="9"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>